--- a/GameData/tables/06_Gacha.xlsx
+++ b/GameData/tables/06_Gacha.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'gacha'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'gacha_pool'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'gacha_pool'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'gear_gacha'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -693,11 +693,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -780,11 +780,11 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>340</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -793,11 +793,11 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>ac</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>340</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -806,11 +806,11 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>340</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9">
@@ -819,11 +819,11 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>340</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>stove</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>340</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -845,11 +845,11 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>stove</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -858,11 +858,11 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>robot</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13">
@@ -871,11 +871,11 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>router</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -884,15 +884,67 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>robot</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>fan</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
           <t>gen</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>2000</v>
+      <c r="C17" s="5" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
